--- a/output/stock_quant_scores/LMT_income_df.xlsx
+++ b/output/stock_quant_scores/LMT_income_df.xlsx
@@ -1092,7 +1092,9 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>8119000000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1102,10 +1104,14 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>22.85</v>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>6315000000</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>-55000000</v>
@@ -1120,9 +1126,13 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>9061000000</v>
+      </c>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>67044000000</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
